--- a/Assets/Data/Buildings.xlsx
+++ b/Assets/Data/Buildings.xlsx
@@ -39,7 +39,7 @@
     <t>NeedBuildingId</t>
   </si>
   <si>
-    <t>Alcana</t>
+    <t>symbol_church</t>
   </si>
   <si>
     <t>Text</t>
@@ -80,9 +80,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -101,6 +101,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -108,8 +138,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -117,22 +178,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -140,35 +193,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -191,14 +215,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -216,14 +232,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -232,14 +240,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,187 +254,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -445,6 +445,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -465,9 +489,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -487,32 +528,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,26 +545,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -553,145 +553,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Buildings.xlsx
+++ b/Assets/Data/Buildings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Buildings" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -70,6 +70,36 @@
   </si>
   <si>
     <t>Period経過時(Nu)を4入手</t>
+  </si>
+  <si>
+    <t>炎の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の炎属性適性をアップ</t>
+  </si>
+  <si>
+    <t>稲妻の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の雷属性適性をアップ</t>
+  </si>
+  <si>
+    <t>蒼の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の氷属性適性をアップ</t>
+  </si>
+  <si>
+    <t>光の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の光属性適性をアップ</t>
+  </si>
+  <si>
+    <t>月の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の闇属性適性をアップ</t>
   </si>
   <si>
     <t>Type</t>
@@ -80,9 +110,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -101,6 +131,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -109,83 +153,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,6 +221,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -238,8 +252,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,13 +284,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -272,61 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -338,24 +440,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -368,73 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,21 +487,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -483,32 +498,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -537,6 +526,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -545,6 +549,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -553,145 +583,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1139,6 +1169,121 @@
         <v>1010</v>
       </c>
     </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>3000</v>
+      </c>
+      <c r="B6">
+        <v>3000</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>320030</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>3010</v>
+      </c>
+      <c r="B7">
+        <v>3010</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>320040</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>3020</v>
+      </c>
+      <c r="B8">
+        <v>3020</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>320050</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>3030</v>
+      </c>
+      <c r="B9">
+        <v>3030</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>320060</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>3040</v>
+      </c>
+      <c r="B10">
+        <v>3040</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10">
+        <v>320070</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
     <row r="28" spans="6:6">
       <c r="F28" s="1"/>
     </row>
@@ -1169,8 +1314,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
     <col min="3" max="3" width="30.0909090909091" customWidth="1"/>
@@ -1229,6 +1374,61 @@
       </c>
       <c r="C5" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>3000</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>3010</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>3020</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>3030</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>3040</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1448,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Buildings.xlsx
+++ b/Assets/Data/Buildings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Buildings" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -48,7 +48,7 @@
     <t>Help</t>
   </si>
   <si>
-    <t>訓練施設Lv1</t>
+    <t>訓練所Lv1</t>
   </si>
   <si>
     <t>Period経過時Lvの低い3人までExp+25</t>
@@ -60,7 +60,13 @@
     <t>Period経過時(Nu)を2入手</t>
   </si>
   <si>
-    <t>訓練施設Lv2</t>
+    <t>資料館Lv1</t>
+  </si>
+  <si>
+    <t>Lv10以下の仲間のバトル入手経験値を+50%</t>
+  </si>
+  <si>
+    <t>訓練所Lv2</t>
   </si>
   <si>
     <t>Period経過時Lvの低い3人までExp+50</t>
@@ -70,6 +76,12 @@
   </si>
   <si>
     <t>Period経過時(Nu)を4入手</t>
+  </si>
+  <si>
+    <t>資料館Lv2</t>
+  </si>
+  <si>
+    <t>Lv20以下の仲間のバトル入手経験値を+50%</t>
   </si>
   <si>
     <t>炎の祭壇</t>
@@ -111,9 +123,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -132,6 +144,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -139,59 +165,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -222,6 +241,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -246,30 +273,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,31 +296,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -320,19 +428,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,127 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -475,15 +487,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -526,6 +529,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -550,6 +564,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -564,17 +587,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -583,7 +595,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -592,7 +604,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -604,124 +616,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1051,7 +1063,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1079,10 +1091,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="B2">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -1102,10 +1114,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="B3">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -1125,25 +1137,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>2000</v>
+        <v>1030</v>
       </c>
       <c r="B4">
-        <v>2000</v>
+        <v>1030</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>320010</v>
+        <v>320030</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1163,7 +1175,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>320020</v>
+        <v>320011</v>
       </c>
       <c r="G5">
         <v>1010</v>
@@ -1171,56 +1183,56 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>3000</v>
+        <v>2020</v>
       </c>
       <c r="B6">
-        <v>3000</v>
+        <v>2020</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>320030</v>
+        <v>320021</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B7">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>320040</v>
+        <v>320031</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B8">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -1232,7 +1244,7 @@
         <v>20</v>
       </c>
       <c r="F8">
-        <v>320050</v>
+        <v>321010</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1240,10 +1252,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B9">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
@@ -1255,7 +1267,7 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>320060</v>
+        <v>321020</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1263,10 +1275,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B10">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -1278,14 +1290,57 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>320070</v>
+        <v>321030</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="6:6">
-      <c r="F28" s="1"/>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>3040</v>
+      </c>
+      <c r="B11">
+        <v>3040</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>321040</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>3050</v>
+      </c>
+      <c r="B12">
+        <v>3050</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>321050</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="6:6">
       <c r="F29" s="1"/>
@@ -1304,6 +1359,9 @@
     </row>
     <row r="34" spans="6:6">
       <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="6:6">
+      <c r="F35" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1314,7 +1372,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1334,7 +1392,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1345,7 +1403,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -1356,7 +1414,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2000</v>
+        <v>1030</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
@@ -1378,7 +1436,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>3000</v>
+        <v>2020</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -1389,7 +1447,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -1400,7 +1458,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -1411,7 +1469,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -1422,13 +1480,35 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>3040</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>3050</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1448,7 +1528,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Buildings.xlsx
+++ b/Assets/Data/Buildings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Buildings" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -81,7 +81,31 @@
     <t>資料館Lv2</t>
   </si>
   <si>
+    <t>Lv15以下の仲間のバトル入手経験値を+50%</t>
+  </si>
+  <si>
+    <t>訓練所Lv3</t>
+  </si>
+  <si>
+    <t>Period経過時Lvの低い3人までExp+75</t>
+  </si>
+  <si>
+    <t>研究施設Lv3</t>
+  </si>
+  <si>
+    <t>Period経過時(Nu)を6入手</t>
+  </si>
+  <si>
+    <t>資料館Lv3</t>
+  </si>
+  <si>
     <t>Lv20以下の仲間のバトル入手経験値を+50%</t>
+  </si>
+  <si>
+    <t>潜伏技術Lv1</t>
+  </si>
+  <si>
+    <t>ステージ探索猶予+10ターン</t>
   </si>
   <si>
     <t>炎の祭壇</t>
@@ -122,10 +146,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -144,80 +168,89 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,25 +264,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,15 +298,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,187 +320,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,6 +529,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -520,22 +553,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -557,8 +594,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -568,22 +607,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,145 +619,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1063,7 +1087,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1241,13 +1265,13 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>321010</v>
+        <v>320012</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1264,13 +1288,13 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>321020</v>
+        <v>320022</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1287,13 +1311,13 @@
         <v>3</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>321030</v>
+        <v>320032</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1310,10 +1334,10 @@
         <v>3</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>321040</v>
+        <v>320040</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1321,38 +1345,118 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>3050</v>
+        <v>4010</v>
       </c>
       <c r="B12">
-        <v>3050</v>
+        <v>4010</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>20</v>
       </c>
       <c r="F12">
-        <v>321050</v>
+        <v>321010</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="6:6">
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="6:6">
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="6:6">
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="6:6">
-      <c r="F32" s="1"/>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>4020</v>
+      </c>
+      <c r="B13">
+        <v>4020</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+      <c r="F13">
+        <v>321020</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>4030</v>
+      </c>
+      <c r="B14">
+        <v>4030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="F14">
+        <v>321030</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>4040</v>
+      </c>
+      <c r="B15">
+        <v>4040</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>321040</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>4050</v>
+      </c>
+      <c r="B16">
+        <v>4050</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+      <c r="F16">
+        <v>321050</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="6:6">
       <c r="F33" s="1"/>
@@ -1362,6 +1466,18 @@
     </row>
     <row r="35" spans="6:6">
       <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="6:6">
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="6:6">
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="6:6">
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="6:6">
+      <c r="F39" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1372,7 +1488,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1502,13 +1618,57 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>3050</v>
+        <v>4010</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>4020</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>4030</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>4040</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>4050</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1528,7 +1688,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Buildings.xlsx
+++ b/Assets/Data/Buildings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Buildings" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
   <si>
     <t>Id</t>
   </si>
@@ -54,88 +54,112 @@
     <t>Period経過時Lvの低い3人までExp+25</t>
   </si>
   <si>
+    <t>訓練所Lv2</t>
+  </si>
+  <si>
+    <t>Period経過時Lvの低い3人までExp+50</t>
+  </si>
+  <si>
+    <t>訓練所Lv3</t>
+  </si>
+  <si>
+    <t>Period経過時Lvの低い3人までExp+75</t>
+  </si>
+  <si>
     <t>研究施設Lv1</t>
   </si>
   <si>
     <t>Period経過時(Nu)を2入手</t>
   </si>
   <si>
+    <t>研究施設Lv2</t>
+  </si>
+  <si>
+    <t>Period経過時(Nu)を4入手</t>
+  </si>
+  <si>
+    <t>研究施設Lv3</t>
+  </si>
+  <si>
+    <t>Period経過時(Nu)を6入手</t>
+  </si>
+  <si>
     <t>資料館Lv1</t>
   </si>
   <si>
     <t>Lv10以下の仲間のバトル入手経験値を+50%</t>
   </si>
   <si>
-    <t>訓練所Lv2</t>
-  </si>
-  <si>
-    <t>Period経過時Lvの低い3人までExp+50</t>
-  </si>
-  <si>
-    <t>研究施設Lv2</t>
-  </si>
-  <si>
-    <t>Period経過時(Nu)を4入手</t>
-  </si>
-  <si>
     <t>資料館Lv2</t>
   </si>
   <si>
     <t>Lv15以下の仲間のバトル入手経験値を+50%</t>
   </si>
   <si>
-    <t>訓練所Lv3</t>
-  </si>
-  <si>
-    <t>Period経過時Lvの低い3人までExp+75</t>
-  </si>
-  <si>
-    <t>研究施設Lv3</t>
-  </si>
-  <si>
-    <t>Period経過時(Nu)を6入手</t>
-  </si>
-  <si>
     <t>資料館Lv3</t>
   </si>
   <si>
     <t>Lv20以下の仲間のバトル入手経験値を+50%</t>
   </si>
   <si>
+    <t>炎の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の炎属性適性をアップ</t>
+  </si>
+  <si>
+    <t>稲妻の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の雷属性適性をアップ</t>
+  </si>
+  <si>
+    <t>蒼の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の氷属性適性をアップ</t>
+  </si>
+  <si>
+    <t>光の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の光属性適性をアップ</t>
+  </si>
+  <si>
+    <t>月の祭壇</t>
+  </si>
+  <si>
+    <t>仲間全員の闇属性適性をアップ</t>
+  </si>
+  <si>
     <t>潜伏技術Lv1</t>
   </si>
   <si>
     <t>ステージ探索猶予+10ターン</t>
   </si>
   <si>
-    <t>炎の祭壇</t>
-  </si>
-  <si>
-    <t>仲間全員の炎属性適性をアップ</t>
-  </si>
-  <si>
-    <t>稲妻の祭壇</t>
-  </si>
-  <si>
-    <t>仲間全員の雷属性適性をアップ</t>
-  </si>
-  <si>
-    <t>蒼の祭壇</t>
-  </si>
-  <si>
-    <t>仲間全員の氷属性適性をアップ</t>
-  </si>
-  <si>
-    <t>光の祭壇</t>
-  </si>
-  <si>
-    <t>仲間全員の光属性適性をアップ</t>
-  </si>
-  <si>
-    <t>月の祭壇</t>
-  </si>
-  <si>
-    <t>仲間全員の闇属性適性をアップ</t>
+    <t>食糧庫Lv1</t>
+  </si>
+  <si>
+    <t>仲間全員の最大Hpが5アップ</t>
+  </si>
+  <si>
+    <t>攻撃技術Lv1</t>
+  </si>
+  <si>
+    <t>仲間全員のATKが2アップ</t>
+  </si>
+  <si>
+    <t>防御技術Lv1</t>
+  </si>
+  <si>
+    <t>仲間全員のDEFが2アップ</t>
+  </si>
+  <si>
+    <t>詠唱技術Lv1</t>
+  </si>
+  <si>
+    <t>仲間全員のSPDが2アップ</t>
   </si>
   <si>
     <t>Type</t>
@@ -146,9 +170,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -167,8 +191,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -176,13 +208,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -196,6 +221,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -204,6 +252,66 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -221,90 +329,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -320,19 +344,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,163 +482,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,6 +535,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -531,9 +570,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -553,6 +594,33 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -567,50 +635,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -619,40 +643,40 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -661,103 +685,103 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1124,7 +1148,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -1147,16 +1171,16 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>320020</v>
+        <v>320011</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1170,16 +1194,16 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>320030</v>
+        <v>320012</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1193,16 +1217,16 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>320011</v>
+        <v>320020</v>
       </c>
       <c r="G5">
-        <v>1010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1216,7 +1240,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1225,7 +1249,7 @@
         <v>320021</v>
       </c>
       <c r="G6">
-        <v>1020</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1239,16 +1263,16 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>320031</v>
+        <v>320022</v>
       </c>
       <c r="G7">
-        <v>1030</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1268,10 +1292,10 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>320012</v>
+        <v>320030</v>
       </c>
       <c r="G8">
-        <v>2010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1285,16 +1309,16 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>320022</v>
+        <v>320031</v>
       </c>
       <c r="G9">
-        <v>2020</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1308,7 +1332,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1317,27 +1341,27 @@
         <v>320032</v>
       </c>
       <c r="G10">
-        <v>2030</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>3040</v>
+        <v>4010</v>
       </c>
       <c r="B11">
-        <v>3040</v>
+        <v>4010</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>320040</v>
+        <v>321010</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1345,10 +1369,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="B12">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
@@ -1360,7 +1384,7 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>321010</v>
+        <v>321020</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1368,10 +1392,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="B13">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -1383,7 +1407,7 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>321020</v>
+        <v>321030</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1391,10 +1415,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>4030</v>
+        <v>4040</v>
       </c>
       <c r="B14">
-        <v>4030</v>
+        <v>4040</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -1406,7 +1430,7 @@
         <v>20</v>
       </c>
       <c r="F14">
-        <v>321030</v>
+        <v>321040</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1414,10 +1438,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>4040</v>
+        <v>4050</v>
       </c>
       <c r="B15">
-        <v>4040</v>
+        <v>4050</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -1429,7 +1453,7 @@
         <v>20</v>
       </c>
       <c r="F15">
-        <v>321040</v>
+        <v>321050</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1437,24 +1461,116 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>4050</v>
+        <v>5010</v>
       </c>
       <c r="B16">
-        <v>4050</v>
+        <v>5010</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F16">
-        <v>321050</v>
+        <v>320040</v>
       </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>6010</v>
+      </c>
+      <c r="B17">
+        <v>6010</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>322010</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>7010</v>
+      </c>
+      <c r="B18">
+        <v>7010</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>15</v>
+      </c>
+      <c r="F18">
+        <v>322020</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>8010</v>
+      </c>
+      <c r="B19">
+        <v>8010</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <v>322030</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>9010</v>
+      </c>
+      <c r="B20">
+        <v>9010</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+      <c r="F20">
+        <v>322040</v>
+      </c>
+      <c r="G20">
         <v>0</v>
       </c>
     </row>
@@ -1488,7 +1604,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="13.7272727272727" customWidth="1"/>
@@ -1607,7 +1723,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>3040</v>
+        <v>4010</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
@@ -1618,7 +1734,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1629,7 +1745,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
@@ -1640,7 +1756,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>4030</v>
+        <v>4040</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -1651,7 +1767,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>4040</v>
+        <v>4050</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
@@ -1662,13 +1778,57 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>4050</v>
+        <v>5010</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>6010</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>7010</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>8010</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>9010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1688,7 +1848,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
